--- a/appointment_forms/042_skincare_trainer_orientation_appointment--appointment_forms.xlsx
+++ b/appointment_forms/042_skincare_trainer_orientation_appointment--appointment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'morning',_'value':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Morning', 'value': 'morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'afternoon',_'value':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Afternoon', 'value': 'afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'evening',_'value':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Evening', 'value': 'evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'skincare',_'value':_'skincare'}</t>
+          <t>skincare</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Skincare', 'value': 'skincare'}</t>
+          <t>Skincare</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'haircare',_'value':_'haircare'}</t>
+          <t>haircare</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Haircare', 'value': 'haircare'}</t>
+          <t>Haircare</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'nailcare',_'value':_'nailcare'}</t>
+          <t>nailcare</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Nailcare', 'value': 'nailcare'}</t>
+          <t>Nailcare</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'spa',_'value':_'spa'}</t>
+          <t>spa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Spa', 'value': 'spa'}</t>
+          <t>Spa</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'salon',_'value':_'salon'}</t>
+          <t>salon</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Salon', 'value': 'salon'}</t>
+          <t>Salon</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'academy',_'value':_'academy'}</t>
+          <t>academy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Academy', 'value': 'academy'}</t>
+          <t>Academy</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_'yes'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': 'yes'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_'no'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': 'no'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
